--- a/KI_Pflege_Anwendungsbeispiele.xlsx
+++ b/KI_Pflege_Anwendungsbeispiele.xlsx
@@ -8,47 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sami.badr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C1E6EDC-860B-4D4C-9940-DB2F732EB4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DE8842-A01F-4843-97A0-F273A4256638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anwendungen" sheetId="1" r:id="rId1"/>
-    <sheet name="Visualisierung" sheetId="3" r:id="rId2"/>
-    <sheet name="Listen &amp; Hinweise" sheetId="2" r:id="rId3"/>
+    <sheet name="Listen &amp; Hinweise" sheetId="3" r:id="rId2"/>
+    <sheet name="Änderungsprotokoll" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anwendungen!$A$1:$J$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Änderungsprotokoll!$A$1:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anwendungen!$A$1:$L$101</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Anwendungen!$1:$1</definedName>
-    <definedName name="KITyp">'Listen &amp; Hinweise'!$B$15:$B$20</definedName>
-    <definedName name="Liste_Umsetzungsstatus">'Listen &amp; Hinweise'!$B$22:$B$28</definedName>
-    <definedName name="Pflegesetting">'Listen &amp; Hinweise'!$B$2:$B$6</definedName>
-    <definedName name="Prozesstyp">'Listen &amp; Hinweise'!$B$8:$B$13</definedName>
+    <definedName name="Kategorie">'Listen &amp; Hinweise'!$B$5:$B$7</definedName>
+    <definedName name="KITyp">'Listen &amp; Hinweise'!$B$19:$B$22</definedName>
+    <definedName name="Ort">'Listen &amp; Hinweise'!$B$2:$B$3</definedName>
+    <definedName name="Pflegesetting">'Listen &amp; Hinweise'!$B$9:$B$12</definedName>
+    <definedName name="Prozesstyp">'Listen &amp; Hinweise'!$B$14:$B$17</definedName>
+    <definedName name="Status_Forschungsprojekt">'Listen &amp; Hinweise'!$B$28:$B$30</definedName>
+    <definedName name="Status_Studie">'Listen &amp; Hinweise'!$B$32:$B$33</definedName>
+    <definedName name="Status_Unternehmen">'Listen &amp; Hinweise'!$B$24:$B$26</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author/>
+    <author>Whitepaper KI &amp; Pflegenotstand</author>
   </authors>
   <commentList>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -61,7 +50,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>WO? Pflegeheim, Pflegedienst oder Klinik.</t>
+          <t>Sitz des Anbieters / Trägers: Deutschland oder Rest der Welt.</t>
         </r>
       </text>
     </comment>
@@ -75,7 +64,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>WOFÜR? Pflegen, Versorgen, Organisieren oder Kommunizieren.</t>
+          <t>WO? Pflegeheim, Pflegedienst, Klinik oder Informell (Pflege durch Angehörige / Nahestehende zu Hause). Bei mehreren Settings bitte das Hauptsetting wählen.</t>
         </r>
       </text>
     </comment>
@@ -89,7 +78,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>WOMIT? Robotik, Sprache + Text, Bild + Sensorik oder Prognose + Optimierung.</t>
+          <t>WOFÜR? Pflegen, Versorgen, Organisieren oder Kommunizieren. Bei mehreren Prozessen bitte den Hauptprozess wählen.</t>
         </r>
       </text>
     </comment>
@@ -103,8 +92,38 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Praxiseinsatz, Pilot, Forschungsprojekt
-</t>
+          <t>WOMIT? Robotik, Sprache + Text, Bild + Sensorik oder Prognose + Optimierung. Bei mehreren KI-Typen bitte den Haupttyp wählen.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Unternehmen, Forschungsprojekt oder Studie. Die Auswahl steuert die Werte im Feld Umsetzungsstatus.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Abhängig von der Kategorie:
+Unternehmen: In Entwicklung / Pilot, Im Verkauf / im Einsatz, Eingestellt
+Forschungsprojekt: In Planung, Laufend, Abgeschlossen
+Studie: Veröffentlicht, Preprint</t>
         </r>
       </text>
     </comment>
@@ -113,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="263">
   <si>
     <t>ID</t>
   </si>
@@ -127,6 +146,9 @@
     <t>Anbieter / Träger</t>
   </si>
   <si>
+    <t>Ort</t>
+  </si>
+  <si>
     <t>Pflege-Setting</t>
   </si>
   <si>
@@ -136,166 +158,88 @@
     <t>KI-Typ</t>
   </si>
   <si>
+    <t>Kategorie</t>
+  </si>
+  <si>
     <t>Umsetzungsstatus</t>
   </si>
   <si>
-    <t>Dropdown-Liste</t>
-  </si>
-  <si>
-    <t>Werte</t>
-  </si>
-  <si>
-    <t>Hinweise zur Nutzung</t>
-  </si>
-  <si>
-    <t>Pflegeheim</t>
-  </si>
-  <si>
-    <t>Die Vorlage ist bewusst kompakt: Die drei Framework-Dimensionen stehen im Zentrum.</t>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPWUFKI </t>
+  </si>
+  <si>
+    <t>intelligentes System, das ambulant Pflegende bei der Versorgung des diabetischen Fußsyndroms unterstützt. Ein KI-basiertes Tool unterstützt präzise bei regelmäßigen Tätigkeiten wie dem Vermessen von Wunden. Die KI kombiniert die erhobenen Informationen mit den von den Verbandssensoren gesammelten Daten, analysiert sie und generiert daraus pflegerelevante Informationen wie z. B. den optimalen Zeitpunkt des nächsten Verbandswechsels, Wundverläufe und -bewertungen.</t>
+  </si>
+  <si>
+    <t>Hochschule Niederrhein</t>
+  </si>
+  <si>
+    <t>Deutschland</t>
   </si>
   <si>
     <t>Pflegedienst</t>
   </si>
   <si>
-    <t>Bei mehreren Settings, Prozess- oder KI-Typen bitte „Mehrere …“ wählen und die konkrete Kombination im Kommentar ergänzen.</t>
+    <t>Organisieren</t>
+  </si>
+  <si>
+    <t>Bild + Sensorik</t>
+  </si>
+  <si>
+    <t>Forschungsprojekt</t>
+  </si>
+  <si>
+    <t>Abgeschlossen</t>
+  </si>
+  <si>
+    <t>https://www.interaktive-technologien.de/service/ergebnissteckbriefe/kip/epwufki</t>
+  </si>
+  <si>
+    <t>Volumen 1,68 Mio. € (davon 81% Förderanteil durch BMBF); Laufzeit 03/2022 - 02/2025</t>
+  </si>
+  <si>
+    <t>KIADEKU</t>
+  </si>
+  <si>
+    <t>KI-System, das Pflegefachpersonen beim Wundmanagement unterstützt. Es hilft bei der korrekten Wundbeurteilung und evidenzbasierten Pflegeplanung und vereinfacht die Wunddokumentation.</t>
+  </si>
+  <si>
+    <t>Universitätsklinikum Essen</t>
   </si>
   <si>
     <t>Klinik</t>
   </si>
   <si>
-    <t>Im Feld „Umsetzungsstatus“ bitte zwischen laufendem Einsatz, Pilot, umgesetztem Forschungsprojekt und Prototyp unterscheiden.</t>
-  </si>
-  <si>
-    <t>Settingübergreifend</t>
-  </si>
-  <si>
-    <t>Link / Quelle kann eine Projektwebsite, Publikation, Evaluation oder Produktseite enthalten.</t>
-  </si>
-  <si>
-    <t>Sonstiges / unklar</t>
-  </si>
-  <si>
-    <t>Nicht auffindbare Angaben bitte mit „Sonstiges / unklar“ bzw. „Unklar“ markieren, damit Datenlücken sichtbar bleiben.</t>
-  </si>
-  <si>
-    <t>Pflegen</t>
-  </si>
-  <si>
-    <t>Versorgen</t>
-  </si>
-  <si>
-    <t>Organisieren</t>
-  </si>
-  <si>
-    <t>Kommunizieren</t>
-  </si>
-  <si>
-    <t>Mehrere Prozess-Typen</t>
-  </si>
-  <si>
-    <t>Robotik</t>
-  </si>
-  <si>
-    <t>Sprache + Text</t>
-  </si>
-  <si>
-    <t>Bild + Sensorik</t>
+    <t>https://kiadeku.ikim.nrw/</t>
+  </si>
+  <si>
+    <t>Volumen 1,59 Mio. € (davon 97% Förderanteil durch BMBF); Laufzeit 03/2022 - 02/2025</t>
+  </si>
+  <si>
+    <t>KIDELIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technologie entwickelt, die das individuelle Risiko für Delire erkennt. Delire sind Zustände akuter kognitiver Verwirrtheit, die durch körperliche oder psychische Stressfaktoren ausgelöst werden. Das hybride, auf Künstlicher Intelligenz (KI) basierende System unterstützt bei der Bewertung des Delirrisikos stationär versorgter Patientinnen und Patienten. </t>
+  </si>
+  <si>
+    <t>Universitätsklinikum Freiburg</t>
   </si>
   <si>
     <t>Prognose + Optimierung</t>
   </si>
   <si>
-    <t>Mehrere KI-Typen</t>
-  </si>
-  <si>
-    <t>Im laufenden Einsatz</t>
-  </si>
-  <si>
-    <t>Pilot / Praxistest</t>
-  </si>
-  <si>
-    <t>Forschungsprojekt umgesetzt</t>
-  </si>
-  <si>
-    <t>Prototyp / Demonstrator</t>
-  </si>
-  <si>
-    <t>Konzept / frühe Entwicklung</t>
-  </si>
-  <si>
-    <t>Beendet / nicht mehr aktiv</t>
-  </si>
-  <si>
-    <t>Unklar</t>
-  </si>
-  <si>
-    <t>Kommentar</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>voize</t>
-  </si>
-  <si>
-    <t>Offline-Spracherkennung spart bis zu 27 % Dokumentationszeit im Heimvoize</t>
-  </si>
-  <si>
-    <t>voize.ai</t>
-  </si>
-  <si>
-    <t>Mehr als 200.000 Pflegekräfte, DSGVO-konform</t>
-  </si>
-  <si>
-    <t>https://www.voize.ai/de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPWUFKI </t>
-  </si>
-  <si>
-    <t>https://www.interaktive-technologien.de/service/ergebnissteckbriefe/kip/epwufki</t>
-  </si>
-  <si>
-    <t>intelligentes System, das ambulant Pflegende bei der Versorgung des diabetischen Fußsyndroms unterstützt. Ein KI-basiertes Tool unterstützt präzise bei regelmäßigen Tätigkeiten wie dem Vermessen von Wunden. Die KI kombiniert die erhobenen Informationen mit den von den Verbandssensoren gesammelten Daten, analysiert sie und generiert daraus pflegerelevante Informationen wie z. B. den optimalen Zeitpunkt des nächsten Verbandswechsels, Wundverläufe und -bewertungen.</t>
-  </si>
-  <si>
-    <t>Volumen 1,68 Mio. € (davon 81% Förderanteil durch BMBF); Laufzeit 03/2022 - 02/2025</t>
-  </si>
-  <si>
-    <t>KIADEKU</t>
-  </si>
-  <si>
-    <t>KI-System, das Pflegefachpersonen beim Wundmanagement unterstützt. Es hilft bei der korrekten Wundbeurteilung und evidenzbasierten Pflegeplanung und vereinfacht die Wunddokumentation.</t>
-  </si>
-  <si>
-    <t>Volumen 1,59 Mio. € (davon 97% Förderanteil durch BMBF); Laufzeit 03/2022 - 02/2025</t>
-  </si>
-  <si>
-    <t>https://kiadeku.ikim.nrw/</t>
-  </si>
-  <si>
-    <t>KIDELIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technologie entwickelt, die das individuelle Risiko für Delire erkennt. Delire sind Zustände akuter kognitiver Verwirrtheit, die durch körperliche oder psychische Stressfaktoren ausgelöst werden. Das hybride, auf Künstlicher Intelligenz (KI) basierende System unterstützt bei der Bewertung des Delirrisikos stationär versorgter Patientinnen und Patienten. </t>
-  </si>
-  <si>
-    <t>Hochschule Niederrhein</t>
-  </si>
-  <si>
-    <t>Universitätsklinikum Essen</t>
-  </si>
-  <si>
-    <t>Universitätsklinikum Freiburg</t>
+    <t>https://www.interaktive-technologien.de/projekte/kidelir</t>
   </si>
   <si>
     <t xml:space="preserve">
 Volumen 2,23 Mio. € (davon 95% Förderanteil durch BMBF) Laufzeit 03/2022 - 01/2025</t>
   </si>
   <si>
-    <t>https://www.interaktive-technologien.de/projekte/kidelir</t>
-  </si>
-  <si>
     <t>KIP-SDM</t>
   </si>
   <si>
@@ -336,13 +280,16 @@
     <t xml:space="preserve"> Fraunhofer-Institut für Software- und Systemtechnik (ISST), Dortmund </t>
   </si>
   <si>
+    <t>Pflegeheim</t>
+  </si>
+  <si>
+    <t>https://www.interaktive-technologien.de/service/ergebnissteckbriefe/kip/pflip</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Volumen 1,9 Mio. € (davon 85% Förderanteil durch BMBF) Laufzeit 03/2022 - 02/2025</t>
   </si>
   <si>
-    <t>https://www.interaktive-technologien.de/service/ergebnissteckbriefe/kip/pflip</t>
-  </si>
-  <si>
     <t>PYSA</t>
   </si>
   <si>
@@ -350,12 +297,36 @@
   </si>
   <si>
     <t xml:space="preserve"> voize </t>
+  </si>
+  <si>
+    <t>Sprache + Text</t>
+  </si>
+  <si>
+    <t>https://www.voize.ai/de</t>
   </si>
   <si>
     <t xml:space="preserve">
 Volumen 1,98 Mio. € (davon 86% Förderanteil durch BMBF) Laufzeit 03/2022 - 01/2025</t>
   </si>
   <si>
+    <t>voize</t>
+  </si>
+  <si>
+    <t>Offline-Spracherkennung spart bis zu 27 % Dokumentationszeit im Heimvoize</t>
+  </si>
+  <si>
+    <t>voize.ai</t>
+  </si>
+  <si>
+    <t>Unternehmen</t>
+  </si>
+  <si>
+    <t>Im Verkauf / im Einsatz</t>
+  </si>
+  <si>
+    <t>Mehr als 200.000 Pflegekräfte, DSGVO-konform</t>
+  </si>
+  <si>
     <t>iPAB</t>
   </si>
   <si>
@@ -378,6 +349,9 @@
     <t xml:space="preserve">Um Muster zu erkennen, die auf ein erhöhtes Risiko unerwünschter medikationsbedingter Ereignisse, insbesondere von Stürzen, hinweisen, nutzen sie Verfahren des maschinellen Lernens (ML) und generative Künstliche Intelligenz (KI). Dieses Vorhersagemodell integrieren die Forschenden in die bestehende Medikationssoftware und entwickeln eine verständliche Warnanzeige. </t>
   </si>
   <si>
+    <t>Laufend</t>
+  </si>
+  <si>
     <t>https://www.interaktive-technologien.de/projekte/emre-ki</t>
   </si>
   <si>
@@ -391,6 +365,12 @@
     <t>In einem ko-kreativen Prozess entwickelt das Projektteam eine Virtual Reality (VR)-Anwendung zur Simulation von Pflegesituationen. Die Technologie legt einen besonderen Fokus auf psychische Belastungsfaktoren und soll es Personen in Pflegeberufen ermöglichen, deren Auslöser und Folgen thematisch zu bearbeiten.</t>
   </si>
   <si>
+    <t>Martin-Luther-Universität Halle-Wittenberg</t>
+  </si>
+  <si>
+    <t>Kommunizieren</t>
+  </si>
+  <si>
     <t>https://www.interaktive-technologien.de/projekte/vreha-pflegesim</t>
   </si>
   <si>
@@ -402,9 +382,6 @@
   </si>
   <si>
     <t>Das Forschungsteam entwickelt ein modular aufgebautes Tele‑Pflegesystem mit Video‑Sprechstunden und optionalen Funktionen wie Wund‑ und Vitaldatenaufnahme.</t>
-  </si>
-  <si>
-    <t>Martin-Luther-Universität Halle-Wittenberg</t>
   </si>
   <si>
     <t>https://www.interaktive-technologien.de/projekte/lift</t>
@@ -461,6 +438,9 @@
     <t xml:space="preserve">MinkTec GmbH, Braunschweig </t>
   </si>
   <si>
+    <t>Pflegen</t>
+  </si>
+  <si>
     <t>https://www.interaktive-technologien.de/projekte/ergofee</t>
   </si>
   <si>
@@ -477,6 +457,9 @@
     <t>Das Forschungsteam entwickelt ein auf erweiterter Realität (Augmented Reality; AR) basierendes Trainingssystem: Über eine Brille zeigt es den Nutzenden eine virtuelle Therapeutin, die Schritt für Schritt physiotherapeutische Übungen anleitet. Während die Nutzenden die Übungen ausführen, analysiert ein auf Künstlicher Intelligenz (KI) gestütztes Modell die Bewegungen in Echtzeit und macht gegebenenfalls Korrekturvorschläge.</t>
   </si>
   <si>
+    <t>Versorgen</t>
+  </si>
+  <si>
     <t>https://www.interaktive-technologien.de/projekte/arkist</t>
   </si>
   <si>
@@ -515,6 +498,9 @@
     <t>Technische Hochschule Mannheim</t>
   </si>
   <si>
+    <t>Robotik</t>
+  </si>
+  <si>
     <t>https://www.interaktive-technologien.de/projekte/selfro</t>
   </si>
   <si>
@@ -604,10 +590,10 @@
     <t>IKAIWu</t>
   </si>
   <si>
+    <t>Das Forschungsteam des Projekts IKIAWu entwickelt ein interaktives System zur Unterstützung von Wunderkennung und -behandlung. Es beinhaltet zum einen eine auf Künstlicher Intelligenz (KI) basierende Bilderkennung, die bisher unterrepräsentierte Wundtypen und -charakteristika berücksichtigt. Darüber hinaus stellt ein interaktiver und KI-basierter Chatbot am „Point of Care“ dermatologisches Expertenwissen sowie leitliniengetreue und evidenzbasierte Informationen zur Verfügung.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> sciendis GmbH, Leipzig </t>
-  </si>
-  <si>
-    <t>Das Forschungsteam des Projekts IKIAWu entwickelt ein interaktives System zur Unterstützung von Wunderkennung und -behandlung. Es beinhaltet zum einen eine auf Künstlicher Intelligenz (KI) basierende Bilderkennung, die bisher unterrepräsentierte Wundtypen und -charakteristika berücksichtigt. Darüber hinaus stellt ein interaktiver und KI-basierter Chatbot am „Point of Care“ dermatologisches Expertenwissen sowie leitliniengetreue und evidenzbasierte Informationen zur Verfügung.</t>
   </si>
   <si>
     <t>https://www.interaktive-technologien.de/projekte/ikiawu</t>
@@ -617,7 +603,7 @@
 Volumen
 1,51 Mio. € (davon 75% Förderanteil durch BMFTR)
 Laufzeit
-09/2025 - 08/2028</t>
+09/2025 - 08/2028 | Zusätzlich: Sprache + Text (KI-Chatbot am Point of Care)</t>
   </si>
   <si>
     <t>SafeWalker</t>
@@ -628,6 +614,9 @@
   <si>
     <t xml:space="preserve">
 Hochschule für Angewandte Wissenschaften Hamburg (HAW Hamburg)</t>
+  </si>
+  <si>
+    <t>Informell</t>
   </si>
   <si>
     <t>https://www.interaktive-technologien.de/projekte/safewalker</t>
@@ -684,12 +673,12 @@
     <t>Atoss Software; Frauenhofer IKS</t>
   </si>
   <si>
+    <t>https://safe-intelligence.fraunhofer.de/artikel/schichtplanungsagent-mit-reinforcement-learning-soll-personaleinsatz-in-krankenh%C3%A4usern-verbessern</t>
+  </si>
+  <si>
     <t>Kein konkreter Pflegebezug</t>
   </si>
   <si>
-    <t>https://safe-intelligence.fraunhofer.de/artikel/schichtplanungsagent-mit-reinforcement-learning-soll-personaleinsatz-in-krankenh%C3%A4usern-verbessern</t>
-  </si>
-  <si>
     <t>curevision</t>
   </si>
   <si>
@@ -702,27 +691,30 @@
     <t>https://curevision.de/pflegeheime-und-ambulante-pflege</t>
   </si>
   <si>
+    <t>ally cares</t>
+  </si>
+  <si>
+    <t>Ally is the UK’s leading evidence-based advanced resident monitoring system for bedroom-based care, giving care teams greater visibility when residents are alone in their bedrooms. Each Ally device uses sensors to capture sound and motion when a resident is alone in their bedroom. AI-powered technology filters background signals to identify resident activity and provide care teams with relevant alerts and insights.</t>
+  </si>
+  <si>
     <t>ally</t>
   </si>
   <si>
-    <t>Ally is the UK’s leading evidence-based advanced resident monitoring system for bedroom-based care, giving care teams greater visibility when residents are alone in their bedrooms. Each Ally device uses sensors to capture sound and motion when a resident is alone in their bedroom. AI-powered technology filters background signals to identify resident activity and provide care teams with relevant alerts and insights.</t>
-  </si>
-  <si>
-    <t>ally cares</t>
+    <t>Rest der Welt</t>
   </si>
   <si>
     <t>www.allycares.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Nobi </t>
+  </si>
+  <si>
+    <t>Smart Lamp mit Optische Sensoren und KI soll Stürze und Bewegungsmuster erkennen und Pflegekräfte alarmieren. Die Lampe kann außerdem nachts beim Aufstehen beleuchten.</t>
+  </si>
+  <si>
     <t>Nobi</t>
   </si>
   <si>
-    <t xml:space="preserve">Nobi </t>
-  </si>
-  <si>
-    <t>Smart Lamp mit Optische Sensoren und KI soll Stürze und Bewegungsmuster erkennen und Pflegekräfte alarmieren. Die Lampe kann außerdem nachts beim Aufstehen beleuchten.</t>
-  </si>
-  <si>
     <t>https://www.nobi.life/de</t>
   </si>
   <si>
@@ -735,12 +727,12 @@
     <t>https://www.homeguardian.ai/</t>
   </si>
   <si>
+    <t>safety ai</t>
+  </si>
+  <si>
     <t xml:space="preserve"> SafelyYou Safety AI™ combines breakthrough AI video technology with clinical expertise, so communities can see how falls happen—and understand how to help keep them from happening again.</t>
   </si>
   <si>
-    <t>safety ai</t>
-  </si>
-  <si>
     <t>safely you</t>
   </si>
   <si>
@@ -768,14 +760,239 @@
     <t>https://www.dexter-health.com/dexter-mobile</t>
   </si>
   <si>
-    <t>Chorddiagramm</t>
+    <t>Dropdown-Liste</t>
+  </si>
+  <si>
+    <t>Werte</t>
+  </si>
+  <si>
+    <t>Hinweise zur Nutzung</t>
+  </si>
+  <si>
+    <t>Pro Zeile eine Anwendung. Die drei Framework-Dimensionen (Pflege-Setting, Prozess-Typ, KI-Typ) stehen im Zentrum.</t>
+  </si>
+  <si>
+    <t>Pflege-Setting, Prozess-Typ und KI-Typ: immer genau einen Wert wählen. Bei mehreren Möglichkeiten den Hauptwert festlegen und Weiteres im Kommentar ergänzen. Es gibt kein „Sonstiges / unklar“ und kein „Settingübergreifend“ mehr.</t>
+  </si>
+  <si>
+    <t>Informell = Pflege zu Hause durch Angehörige / Nahestehende ohne professionellen Pflegedienst.</t>
+  </si>
+  <si>
+    <t>Ort = Sitz des Anbieters / Trägers (Deutschland oder Rest der Welt).</t>
+  </si>
+  <si>
+    <t>Kategorie zuerst wählen: Der Umsetzungsstatus bietet dann nur die passenden Werte an (Unternehmen / Forschungsprojekt / Studie).</t>
+  </si>
+  <si>
+    <t>Studie</t>
+  </si>
+  <si>
+    <t>Umsetzungsstatus Unternehmen: In Entwicklung / Pilot, Im Verkauf / im Einsatz, Eingestellt.</t>
+  </si>
+  <si>
+    <t>Umsetzungsstatus Forschungsprojekt: In Planung, Laufend, Abgeschlossen (bei Förderprojekten anhand der Laufzeit).</t>
+  </si>
+  <si>
+    <t>Umsetzungsstatus Studie: Veröffentlicht oder Preprint.</t>
+  </si>
+  <si>
+    <t>Link / Quelle kann eine Projektwebsite, Publikation, Evaluation oder Produktseite enthalten.</t>
+  </si>
+  <si>
+    <t>Gelb markierte Zellen in „Anwendungen“ sind Vorschläge aus der Überarbeitung und noch zu bestätigen (siehe Blatt „Änderungsprotokoll“). Nach der Prüfung die Füllfarbe entfernen.</t>
+  </si>
+  <si>
+    <t>Status: Unternehmen</t>
+  </si>
+  <si>
+    <t>In Entwicklung / Pilot</t>
+  </si>
+  <si>
+    <t>Eingestellt</t>
+  </si>
+  <si>
+    <t>Status: Forschungsprojekt</t>
+  </si>
+  <si>
+    <t>In Planung</t>
+  </si>
+  <si>
+    <t>Status: Studie</t>
+  </si>
+  <si>
+    <t>Veröffentlicht</t>
+  </si>
+  <si>
+    <t>Preprint</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>Feld</t>
+  </si>
+  <si>
+    <t>Alt</t>
+  </si>
+  <si>
+    <t>Neu</t>
+  </si>
+  <si>
+    <t>Begründung</t>
+  </si>
+  <si>
+    <t>Sicherheit</t>
+  </si>
+  <si>
+    <t>Settingübergreifend</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Träger Universitätsklinikum Essen; Wundmanagement durch Pflegefachpersonen</t>
+  </si>
+  <si>
+    <t>Vorschlag – bitte prüfen</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'stationäre Pflege', Träger Charité</t>
+  </si>
+  <si>
+    <t>Sonstiges / unklar</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Risikovorhersage / Dashboard – gleiche Logik wie KIDELIR, EMRE-KI, ProSSpon</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Datenplattform u. a. mit Smart-Home-Geräten – eher häuslicher Bereich (unsicher)</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Datenplattform / Datenharmonisierung</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Sturzprophylaxe bei Pflegebedürftigen (typisch stationäre Langzeitpflege, unsicher)</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Risikovorhersage + Dashboard zur Planung – gleiche Logik wie ProSSpon</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'klinische Zusammenhänge', Behandlungsprozesse</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Sonstiges / unklar'): VR-Simulation für Pflegeberufe; kein eindeutiges Setting – Klinik als Annahme</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Sonstiges / unklar'): Tele-Pflegesystem mit Video-Sprechstunde (ambulant / Häuslichkeit)</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Video-Sprechstunden / Telepflege</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): AR-Übungstraining für Nutzende, eher häuslich / ambulant (unsicher)</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Wunderkennung am 'Point of Care'; Wundversorgung häufig ambulant (unsicher)</t>
+  </si>
+  <si>
+    <t>Mehrere KI-Typen</t>
+  </si>
+  <si>
+    <t>Haupttyp festgelegt (vorher 'Mehrere KI-Typen'): Bilderkennung von Wunden; Chatbot ist Zusatz (siehe Kommentar)</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Mobilisation / Mobilitätsunterstützung</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): soziale Betreuung / Prävention von Vereinsamung (Prozess-Landkarte: 'Pflegen')</t>
+  </si>
+  <si>
+    <t>Gemeinsames Projekt Fraunhofer IKS + ATOSS Software (Quelle: Fraunhofer-Artikel)</t>
+  </si>
+  <si>
+    <t>Pilot / Praxistest</t>
+  </si>
+  <si>
+    <t>Quelle formuliert in der Vergangenheit ('haben entwickelt'); Laufzeit unbekannt</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Produktseite nennt zuerst 'Pflegeheime und ambulante Pflege'</t>
+  </si>
+  <si>
+    <t>Sitz des Anbieters: Belgien (Sitz Leuven)</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Sturz- und Bewegungserkennung – analog zu ally cares</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Sturz- und Aktivitätserkennung – analog zu ally cares</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Sturzerkennung / Sturzprävention – analog zu ally cares</t>
+  </si>
+  <si>
+    <t>Sitz des Anbieters: Schweiz (vermutet)</t>
+  </si>
+  <si>
+    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Bettausstieg / Sturz erkennen – analog zu ally cares</t>
+  </si>
+  <si>
+    <t>Radar-Sensorik + KI-Bewegungsanalyse (vorher 'Sonstiges / unklar')</t>
+  </si>
+  <si>
+    <t>EPWUFKI</t>
+  </si>
+  <si>
+    <t>Anbieter / Träger sitzt in Deutschland</t>
+  </si>
+  <si>
+    <t>sicher</t>
+  </si>
+  <si>
+    <t>Gefördertes Verbundprojekt (BMBF/BMFTR), Quelle: interaktive-technologien.de</t>
+  </si>
+  <si>
+    <t>Forschungsprojekt umgesetzt</t>
+  </si>
+  <si>
+    <t>Projektlaufzeit endete 2025 (laut Kommentar-Spalte)</t>
+  </si>
+  <si>
+    <t>Kommerzielles Produkt / Anbieter</t>
+  </si>
+  <si>
+    <t>Im laufenden Einsatz</t>
+  </si>
+  <si>
+    <t>Kommerzielles Produkt am Markt</t>
+  </si>
+  <si>
+    <t>Projektlaufzeit läuft noch (laut Kommentar-Spalte)</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Sonstiges / unklar'): Rollator für selbstständige Mobilität im urbanen Raum / Weg nach Hause</t>
+  </si>
+  <si>
+    <t>Laufzeit 11/2024 – 10/2026: endet in diesen Tagen, ggf. bald auf 'Abgeschlossen' setzen</t>
+  </si>
+  <si>
+    <t>Projektlaufzeit endete 02/2026</t>
+  </si>
+  <si>
+    <t>Sitz des Anbieters: Vereinigtes Königreich (UK)</t>
+  </si>
+  <si>
+    <t>Sitz des Anbieters: Australien</t>
+  </si>
+  <si>
+    <t>Sitz des Anbieters: USA</t>
+  </si>
+  <si>
+    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'mehrere Bewohner in einer Aufnahme'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -849,8 +1066,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,8 +1090,19 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -896,12 +1128,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -921,19 +1162,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -947,29 +1177,76 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDDEBF7"/>
+          <bgColor rgb="FFDDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
@@ -1053,133 +1330,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>701896</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>179295</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Grafik 1" descr="Correlation Heatmap Seaborn: Python Correlation Heatmap - NOSXAT">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7E21FC4-AD3D-1D11-6824-AC482990F12B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1524000" y="1524001"/>
-          <a:ext cx="9083896" cy="4560794"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>179294</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>179294</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Grafik 2" descr="Chord diagram - from Data to Viz">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD2F62B4-8A20-D7C7-CB55-5BC055683060}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1524000" y="7239000"/>
-          <a:ext cx="5513294" cy="5513294"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1502,20 +1652,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1541,1106 +1694,1329 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="12"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>13</v>
       </c>
+      <c r="D4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="B6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="L6" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="H7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="J7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="B8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="J8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="B9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="H9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="J9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
+      <c r="B10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="B12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="H12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>84</v>
+      <c r="B13" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>86</v>
+        <v>32</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>90</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>95</v>
-      </c>
       <c r="J15" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>84</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>13</v>
+        <v>89</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>105</v>
+        <v>18</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>110</v>
+        <v>18</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>16</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>114</v>
+        <v>18</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>119</v>
+        <v>54</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="153" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="153" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>11</v>
+        <v>110</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>129</v>
+        <v>112</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>134</v>
+        <v>112</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>139</v>
+        <v>112</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>144</v>
+        <v>112</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="153" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="153" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>149</v>
+      <c r="H26" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="165.75" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>154</v>
-      </c>
       <c r="J27" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="153" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="153" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>163</v>
+        <v>32</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="102" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>165</v>
+      <c r="B30" s="14" t="s">
+        <v>155</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="I30" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="H31" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="L31" s="4"/>
+    </row>
+    <row r="32" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>11</v>
+        <v>171</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>167</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" ht="114.75" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>180</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>167</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2651,10 +3027,12 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="3"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" s="3"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2665,10 +3043,12 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
-      <c r="I39" s="5"/>
+      <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" s="5"/>
+      <c r="L39" s="4"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2679,10 +3059,12 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="3"/>
+      <c r="I40" s="2"/>
       <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" s="3"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2693,10 +3075,12 @@
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
-      <c r="I41" s="5"/>
+      <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" s="5"/>
+      <c r="L41" s="4"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2707,10 +3091,12 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="3"/>
+      <c r="I42" s="2"/>
       <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" s="3"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2721,10 +3107,12 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
+      <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" s="5"/>
+      <c r="L43" s="4"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2735,10 +3123,12 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="3"/>
+      <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" s="3"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2749,10 +3139,12 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
+      <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" s="5"/>
+      <c r="L45" s="4"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2763,10 +3155,12 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="3"/>
+      <c r="I46" s="2"/>
       <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="3"/>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2777,10 +3171,12 @@
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
-      <c r="I47" s="5"/>
+      <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K47" s="5"/>
+      <c r="L47" s="4"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2791,10 +3187,12 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="3"/>
+      <c r="I48" s="2"/>
       <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K48" s="3"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -2805,10 +3203,12 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
-      <c r="I49" s="5"/>
+      <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K49" s="5"/>
+      <c r="L49" s="4"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2819,10 +3219,12 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="I50" s="3"/>
+      <c r="I50" s="2"/>
       <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K50" s="3"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2833,10 +3235,12 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
-      <c r="I51" s="5"/>
+      <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K51" s="5"/>
+      <c r="L51" s="4"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2847,10 +3251,12 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-      <c r="I52" s="3"/>
+      <c r="I52" s="2"/>
       <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" s="3"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -2861,10 +3267,12 @@
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-      <c r="I53" s="5"/>
+      <c r="I53" s="4"/>
       <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" s="5"/>
+      <c r="L53" s="4"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2875,10 +3283,12 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-      <c r="I54" s="3"/>
+      <c r="I54" s="2"/>
       <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K54" s="3"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -2889,10 +3299,12 @@
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
-      <c r="I55" s="5"/>
+      <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K55" s="5"/>
+      <c r="L55" s="4"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2903,10 +3315,12 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-      <c r="I56" s="3"/>
+      <c r="I56" s="2"/>
       <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="3"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -2917,10 +3331,12 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
-      <c r="I57" s="5"/>
+      <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="5"/>
+      <c r="L57" s="4"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2931,10 +3347,12 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-      <c r="I58" s="3"/>
+      <c r="I58" s="2"/>
       <c r="J58" s="2"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="3"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -2945,10 +3363,12 @@
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
-      <c r="I59" s="5"/>
+      <c r="I59" s="4"/>
       <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="5"/>
+      <c r="L59" s="4"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2959,10 +3379,12 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-      <c r="I60" s="3"/>
+      <c r="I60" s="2"/>
       <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="3"/>
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -2973,10 +3395,12 @@
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
-      <c r="I61" s="5"/>
+      <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="5"/>
+      <c r="L61" s="4"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2987,10 +3411,12 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
-      <c r="I62" s="3"/>
+      <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="3"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -3001,10 +3427,12 @@
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
-      <c r="I63" s="5"/>
+      <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="5"/>
+      <c r="L63" s="4"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -3015,10 +3443,12 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-      <c r="I64" s="3"/>
+      <c r="I64" s="2"/>
       <c r="J64" s="2"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K64" s="3"/>
+      <c r="L64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -3029,10 +3459,12 @@
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
-      <c r="I65" s="5"/>
+      <c r="I65" s="4"/>
       <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K65" s="5"/>
+      <c r="L65" s="4"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3043,10 +3475,12 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-      <c r="I66" s="3"/>
+      <c r="I66" s="2"/>
       <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K66" s="3"/>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -3057,10 +3491,12 @@
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
-      <c r="I67" s="5"/>
+      <c r="I67" s="4"/>
       <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K67" s="5"/>
+      <c r="L67" s="4"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3071,10 +3507,12 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
-      <c r="I68" s="3"/>
+      <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K68" s="3"/>
+      <c r="L68" s="2"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -3085,10 +3523,12 @@
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
-      <c r="I69" s="5"/>
+      <c r="I69" s="4"/>
       <c r="J69" s="4"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K69" s="5"/>
+      <c r="L69" s="4"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3099,10 +3539,12 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
-      <c r="I70" s="3"/>
+      <c r="I70" s="2"/>
       <c r="J70" s="2"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K70" s="3"/>
+      <c r="L70" s="2"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -3113,10 +3555,12 @@
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
-      <c r="I71" s="5"/>
+      <c r="I71" s="4"/>
       <c r="J71" s="4"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K71" s="5"/>
+      <c r="L71" s="4"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -3127,10 +3571,12 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
-      <c r="I72" s="3"/>
+      <c r="I72" s="2"/>
       <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K72" s="3"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -3141,10 +3587,12 @@
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
-      <c r="I73" s="5"/>
+      <c r="I73" s="4"/>
       <c r="J73" s="4"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K73" s="5"/>
+      <c r="L73" s="4"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3155,10 +3603,12 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-      <c r="I74" s="3"/>
+      <c r="I74" s="2"/>
       <c r="J74" s="2"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K74" s="3"/>
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -3169,10 +3619,12 @@
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
-      <c r="I75" s="5"/>
+      <c r="I75" s="4"/>
       <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K75" s="5"/>
+      <c r="L75" s="4"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -3183,10 +3635,12 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-      <c r="I76" s="3"/>
+      <c r="I76" s="2"/>
       <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K76" s="3"/>
+      <c r="L76" s="2"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3197,10 +3651,12 @@
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="5"/>
+      <c r="I77" s="4"/>
       <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K77" s="5"/>
+      <c r="L77" s="4"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3211,10 +3667,12 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-      <c r="I78" s="3"/>
+      <c r="I78" s="2"/>
       <c r="J78" s="2"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K78" s="3"/>
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -3225,10 +3683,12 @@
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
-      <c r="I79" s="5"/>
+      <c r="I79" s="4"/>
       <c r="J79" s="4"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K79" s="5"/>
+      <c r="L79" s="4"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3239,10 +3699,12 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-      <c r="I80" s="3"/>
+      <c r="I80" s="2"/>
       <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K80" s="3"/>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -3253,10 +3715,12 @@
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="I81" s="5"/>
+      <c r="I81" s="4"/>
       <c r="J81" s="4"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K81" s="5"/>
+      <c r="L81" s="4"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3267,10 +3731,12 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
-      <c r="I82" s="3"/>
+      <c r="I82" s="2"/>
       <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K82" s="3"/>
+      <c r="L82" s="2"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -3281,10 +3747,12 @@
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
-      <c r="I83" s="5"/>
+      <c r="I83" s="4"/>
       <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K83" s="5"/>
+      <c r="L83" s="4"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3295,10 +3763,12 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
-      <c r="I84" s="3"/>
+      <c r="I84" s="2"/>
       <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K84" s="3"/>
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -3309,10 +3779,12 @@
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
-      <c r="I85" s="5"/>
+      <c r="I85" s="4"/>
       <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K85" s="5"/>
+      <c r="L85" s="4"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3323,10 +3795,12 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-      <c r="I86" s="3"/>
+      <c r="I86" s="2"/>
       <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K86" s="3"/>
+      <c r="L86" s="2"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -3337,10 +3811,12 @@
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
-      <c r="I87" s="5"/>
+      <c r="I87" s="4"/>
       <c r="J87" s="4"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K87" s="5"/>
+      <c r="L87" s="4"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3351,10 +3827,12 @@
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
-      <c r="I88" s="3"/>
+      <c r="I88" s="2"/>
       <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K88" s="3"/>
+      <c r="L88" s="2"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -3365,10 +3843,12 @@
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
-      <c r="I89" s="5"/>
+      <c r="I89" s="4"/>
       <c r="J89" s="4"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K89" s="5"/>
+      <c r="L89" s="4"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3379,10 +3859,12 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="3"/>
+      <c r="I90" s="2"/>
       <c r="J90" s="2"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K90" s="3"/>
+      <c r="L90" s="2"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -3393,10 +3875,12 @@
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
-      <c r="I91" s="5"/>
+      <c r="I91" s="4"/>
       <c r="J91" s="4"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K91" s="5"/>
+      <c r="L91" s="4"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -3407,10 +3891,12 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
-      <c r="I92" s="3"/>
+      <c r="I92" s="2"/>
       <c r="J92" s="2"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K92" s="3"/>
+      <c r="L92" s="2"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -3421,10 +3907,12 @@
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
-      <c r="I93" s="5"/>
+      <c r="I93" s="4"/>
       <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K93" s="5"/>
+      <c r="L93" s="4"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -3435,10 +3923,12 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
-      <c r="I94" s="3"/>
+      <c r="I94" s="2"/>
       <c r="J94" s="2"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K94" s="3"/>
+      <c r="L94" s="2"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -3449,10 +3939,12 @@
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
-      <c r="I95" s="5"/>
+      <c r="I95" s="4"/>
       <c r="J95" s="4"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K95" s="5"/>
+      <c r="L95" s="4"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -3463,10 +3955,12 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-      <c r="I96" s="3"/>
+      <c r="I96" s="2"/>
       <c r="J96" s="2"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K96" s="3"/>
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -3477,10 +3971,12 @@
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
-      <c r="I97" s="5"/>
+      <c r="I97" s="4"/>
       <c r="J97" s="4"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K97" s="5"/>
+      <c r="L97" s="4"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -3491,10 +3987,12 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
-      <c r="I98" s="3"/>
+      <c r="I98" s="2"/>
       <c r="J98" s="2"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K98" s="3"/>
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -3505,10 +4003,12 @@
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
-      <c r="I99" s="5"/>
+      <c r="I99" s="4"/>
       <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K99" s="5"/>
+      <c r="L99" s="4"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -3519,10 +4019,12 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="I100" s="3"/>
+      <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K100" s="3"/>
+      <c r="L100" s="2"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -3533,242 +4035,411 @@
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
-      <c r="I101" s="5"/>
+      <c r="I101" s="4"/>
       <c r="J101" s="4"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J101" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="H4:H101">
+  <autoFilter ref="A1:L101" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="J2:J101">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>OR($J2="Laufend",$J2="Im Verkauf / im Einsatz",$J2="Veröffentlicht")</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$H4="Im laufenden Einsatz"</formula>
+      <formula>OR($J2="In Planung",$J2="In Entwicklung / Pilot",$J2="Preprint")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$H4="Pilot / Praxistest"</formula>
+      <formula>OR($J2="Abgeschlossen")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>$H4="Unklar"</formula>
+      <formula>OR($J2="Eingestellt")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte eine Kategorie auswählen." sqref="F1:F2 F4:F1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Deutschland oder Rest der Welt." sqref="E2:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>Ort</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte ein Hauptsetting auswählen." sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>Pflegesetting</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte einen Hauptprozess auswählen." sqref="G2:G1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Prozesstyp</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte eine Kategorie auswählen." sqref="E1:E2 E4:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>Pflegesetting</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte eine Kategorie auswählen." sqref="G1:G2 G4:G1048576" xr:uid="{2EE5FB9D-F53E-4436-99F0-46B24ACB8242}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte einen Haupt-KI-Typ auswählen." sqref="H2:H1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>KITyp</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Bitte eine Kategorie auswählen." sqref="H1:H2 H4:H1048576" xr:uid="{D3957DE6-8816-418C-8F88-B0816BD0074D}">
-      <formula1>Liste_Umsetzungsstatus</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Unternehmen, Forschungsprojekt oder Studie." sqref="I2:I1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>Kategorie</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ungültige Auswahl" error="Bitte einen Wert aus dem Dropdown-Menü auswählen." promptTitle="Auswahlliste" prompt="Erst Kategorie wählen, dann den passenden Status." sqref="J2:J1048576" xr:uid="{00000000-0002-0000-0000-000005000000}">
+      <formula1>INDIRECT("Status_"&amp;$I2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="I11" r:id="rId1" xr:uid="{FA99EE6B-55D2-4281-8A3D-A83C4FEADA85}"/>
-    <hyperlink ref="I6" r:id="rId2" xr:uid="{65FDE5EB-3177-4E1F-A4D3-F9D4217358F6}"/>
-    <hyperlink ref="I7" r:id="rId3" xr:uid="{F8843B55-7E3A-4BC2-9B87-9D00AAB591A4}"/>
-    <hyperlink ref="I8" r:id="rId4" xr:uid="{B1AAF4B2-B2CF-490D-8821-71CA852A582E}"/>
-    <hyperlink ref="I9" r:id="rId5" xr:uid="{3D044346-2795-48BD-8EDB-A10C0B3E3F19}"/>
-    <hyperlink ref="I10" r:id="rId6" xr:uid="{2BF94D2E-6874-4FC0-8404-F370CA8A8F9F}"/>
-    <hyperlink ref="I12" r:id="rId7" xr:uid="{32175466-1EFE-4BE1-8E30-F98106CA8ABF}"/>
-    <hyperlink ref="I13" r:id="rId8" xr:uid="{778742F5-1AF4-4E61-A12F-15524BE90C2C}"/>
-    <hyperlink ref="I14" r:id="rId9" xr:uid="{F24DE1CE-4C90-4405-9C81-372287E05B3D}"/>
-    <hyperlink ref="I18" r:id="rId10" xr:uid="{D65ADBD6-03DC-4883-A5A7-708859C0E5F0}"/>
-    <hyperlink ref="I19" r:id="rId11" xr:uid="{DF0B6870-F731-418C-A950-26424719C7A0}"/>
-    <hyperlink ref="I22" r:id="rId12" xr:uid="{7E9EB6BA-DD5E-4D5C-BE10-52BA9E1F2186}"/>
-    <hyperlink ref="I27" r:id="rId13" xr:uid="{509EBC5C-648B-4CE6-90CD-CF6B9C549FF1}"/>
-    <hyperlink ref="I33" r:id="rId14" xr:uid="{B9306FDC-A532-4DA6-B7D6-A8CAEB2AE300}"/>
-    <hyperlink ref="I37" r:id="rId15" xr:uid="{2FB83D36-4CCC-4A97-A2A7-5311F662ED2B}"/>
+    <hyperlink ref="I6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I10" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I14" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I18" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I19" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I33" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I37" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
+  <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6316CCD-FFFD-46FF-8BDD-6AB0444BD394}">
-  <dimension ref="C37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
-        <v>196</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="4" max="4" width="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="C10" s="17"/>
+      <c r="D10" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3776,321 +4447,2806 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010063107CA8B5A7434FA88AAD429DD09C74" ma:contentTypeVersion="21" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="85d3e4c670172debd402798e1f9f0405">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c" xmlns:ns3="cd56f89b-ac27-4c6b-9540-7772d6c08fe7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="07be3d46663b0142a603846ae7b31bbe" ns2:_="" ns3:_="">
-    <xsd:import namespace="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c"/>
-    <xsd:import namespace="cd56f89b-ac27-4c6b-9540-7772d6c08fe7"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="18" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="19" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fc58ff6-2a3f-40a3-8d32-e116a35ec156" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cd56f89b-ac27-4c6b-9540-7772d6c08fe7" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f5d2cfef-bc52-4180-8fb0-073759876f91}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="cd56f89b-ac27-4c6b-9540-7772d6c08fe7">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="cd56f89b-ac27-4c6b-9540-7772d6c08fe7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1BFEA58-229A-4722-AEA8-98FBC7DF128F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c"/>
-    <ds:schemaRef ds:uri="cd56f89b-ac27-4c6b-9540-7772d6c08fe7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE5932AA-B3A8-4621-A527-0CDE7AD8D61D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60FB4DBC-EA00-4D1B-B42B-058B1DD1C925}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cd56f89b-ac27-4c6b-9540-7772d6c08fe7"/>
-    <ds:schemaRef ds:uri="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G127"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="80" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
+        <v>4</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
+        <v>6</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>6</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>7</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>7</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>8</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>8</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>11</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>13</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>14</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>14</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>18</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>25</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>25</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>26</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>27</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>29</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>29</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>30</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>32</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>32</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>33</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>34</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>35</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>35</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>35</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>3</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>3</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>3</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>4</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>4</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>4</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>5</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>5</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>5</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
+        <v>6</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
+        <v>6</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
+        <v>6</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
+        <v>7</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>7</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>8</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>8</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
+        <v>8</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
+        <v>9</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
+        <v>9</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
+        <v>9</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
+        <v>10</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
+        <v>10</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
+        <v>10</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="19">
+        <v>11</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="19">
+        <v>11</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="19">
+        <v>11</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="19">
+        <v>12</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="19">
+        <v>12</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
+        <v>12</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="19">
+        <v>13</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="19">
+        <v>13</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="19">
+        <v>13</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="19">
+        <v>14</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="19">
+        <v>14</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="19">
+        <v>14</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="19">
+        <v>15</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="19">
+        <v>15</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="19">
+        <v>15</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="19">
+        <v>16</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="19">
+        <v>16</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="19">
+        <v>16</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G69" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
+        <v>17</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G70" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="19">
+        <v>17</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="19">
+        <v>17</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G72" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="19">
+        <v>18</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="19">
+        <v>18</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G74" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="19">
+        <v>18</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G75" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="19">
+        <v>19</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G76" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="19">
+        <v>19</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="19">
+        <v>19</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G78" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="19">
+        <v>20</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G79" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="19">
+        <v>20</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G80" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="19">
+        <v>20</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G81" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="19">
+        <v>21</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G82" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="19">
+        <v>21</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G83" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="19">
+        <v>21</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G84" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="19">
+        <v>22</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G85" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="19">
+        <v>22</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="19"/>
+      <c r="E86" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G86" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="19">
+        <v>22</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G87" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="19">
+        <v>23</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" s="19"/>
+      <c r="E88" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G88" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="19">
+        <v>23</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G89" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="19">
+        <v>23</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G90" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="19">
+        <v>24</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="19"/>
+      <c r="E91" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G91" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="19">
+        <v>24</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="19"/>
+      <c r="E92" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G92" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="19">
+        <v>24</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F93" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G93" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="19">
+        <v>25</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="19"/>
+      <c r="E94" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G94" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="19">
+        <v>25</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="19"/>
+      <c r="E95" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G95" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="19">
+        <v>25</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G96" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="19">
+        <v>26</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G97" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="19">
+        <v>26</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G98" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="19">
+        <v>26</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F99" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="G99" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="19">
+        <v>26</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F100" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="19">
+        <v>27</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="19"/>
+      <c r="E101" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G101" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="19">
+        <v>27</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="19"/>
+      <c r="E102" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G102" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="19">
+        <v>27</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F103" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="G103" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="19">
+        <v>28</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" s="19"/>
+      <c r="E104" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G104" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="19">
+        <v>28</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="19"/>
+      <c r="E105" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G105" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="19">
+        <v>28</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="G106" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="19">
+        <v>29</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="19"/>
+      <c r="E107" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G107" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="19">
+        <v>30</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="19"/>
+      <c r="E108" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G108" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="19">
+        <v>30</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="19"/>
+      <c r="E109" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F109" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G109" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="19">
+        <v>30</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G110" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="19">
+        <v>31</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="G111" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="19">
+        <v>31</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="19">
+        <v>31</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="19">
+        <v>32</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F114" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G114" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="19">
+        <v>32</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F115" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G115" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="19">
+        <v>33</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D116" s="19"/>
+      <c r="E116" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F116" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="19">
+        <v>33</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G117" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="19">
+        <v>33</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F118" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="19">
+        <v>34</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" s="19"/>
+      <c r="E119" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F119" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="G119" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="19">
+        <v>34</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="19"/>
+      <c r="E120" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F120" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G120" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="19">
+        <v>34</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F121" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="19">
+        <v>35</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="19"/>
+      <c r="E122" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F122" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G122" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="19">
+        <v>35</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F123" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G123" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="19">
+        <v>36</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" s="19"/>
+      <c r="E124" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="G124" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="19">
+        <v>36</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="19"/>
+      <c r="E125" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="G125" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="19">
+        <v>36</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F126" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="G126" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="19">
+        <v>36</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F127" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G127" s="19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G127" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/KI_Pflege_Anwendungsbeispiele.xlsx
+++ b/KI_Pflege_Anwendungsbeispiele.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sami.badr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acatechev.sharepoint.de/sites/Technologie/Freigegebene Dokumente/05 Lernende Systeme/03 AGs/AG 6 Gesundheit/WP KI und Pflegenotstand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DE8842-A01F-4843-97A0-F273A4256638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{578BC691-77EE-41F0-B240-773D70F1C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="267">
   <si>
     <t>ID</t>
   </si>
@@ -141,9 +141,6 @@
   </si>
   <si>
     <t>Kurzbeschreibung / Use Case</t>
-  </si>
-  <si>
-    <t>Anbieter / Träger</t>
   </si>
   <si>
     <t>Ort</t>
@@ -986,6 +983,21 @@
   </si>
   <si>
     <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'mehrere Bewohner in einer Aufnahme'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Digital Case Manager-A Data-Driven Tool to Support Family Caregivers with Initial Guidance </t>
+  </si>
+  <si>
+    <t>This tool uses machine learning algorithms to learn the relationship between a care situation and the next care steps and helps family caregivers balance their professional and private lives so that they are able to continue caring for their family members without sacrificing their own jobs and personal ambitions.</t>
+  </si>
+  <si>
+    <t>Paul Wunderlich, Frauke Wiegräbe, Helene Dörksen</t>
+  </si>
+  <si>
+    <t>Anbieter / Autoren</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/36673969/</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1154,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1213,6 +1225,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1679,31 +1692,31 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1743,37 +1756,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="D4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="10" t="s">
         <v>21</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,37 +1794,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="21" t="s">
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -1819,37 +1832,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="11" t="s">
+      <c r="L6" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -1857,37 +1870,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1895,37 +1908,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="E8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="11" t="s">
+      <c r="L8" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1933,37 +1946,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="23" t="s">
+      <c r="G9" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1971,37 +1984,37 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="11" t="s">
+      <c r="L10" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2009,37 +2022,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2047,37 +2060,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="11" t="s">
+      <c r="L12" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2085,37 +2098,37 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="L13" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -2123,37 +2136,37 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="11" t="s">
+      <c r="L14" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -2161,37 +2174,37 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="5" t="s">
+      <c r="L15" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2199,37 +2212,37 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="E16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2237,37 +2250,37 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="E17" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="5" t="s">
+      <c r="L17" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -2275,37 +2288,37 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="11" t="s">
+      <c r="L18" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2313,37 +2326,37 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K19" s="9" t="s">
+      <c r="L19" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -2351,37 +2364,37 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="153" customHeight="1" x14ac:dyDescent="0.25">
@@ -2389,37 +2402,37 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="E21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="5" t="s">
+      <c r="L21" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2427,37 +2440,37 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="11" t="s">
+      <c r="L22" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -2465,37 +2478,37 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K23" s="5" t="s">
+      <c r="L23" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2503,37 +2516,37 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -2541,37 +2554,37 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K25" s="5" t="s">
+      <c r="L25" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="153" customHeight="1" x14ac:dyDescent="0.25">
@@ -2579,37 +2592,37 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,37 +2630,37 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K27" s="9" t="s">
+      <c r="L27" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="153" customHeight="1" x14ac:dyDescent="0.25">
@@ -2655,37 +2668,37 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2693,37 +2706,37 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="5" t="s">
+      <c r="L29" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
@@ -2731,37 +2744,37 @@
         <v>29</v>
       </c>
       <c r="B30" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2769,34 +2782,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K31" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="L31" s="4"/>
     </row>
@@ -2805,34 +2818,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="L32" s="2"/>
     </row>
@@ -2841,34 +2854,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="L33" s="4"/>
     </row>
@@ -2877,34 +2890,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="L34" s="2"/>
     </row>
@@ -2913,34 +2926,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="L35" s="4"/>
     </row>
@@ -2949,34 +2962,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="L36" s="2"/>
     </row>
@@ -2985,51 +2998,71 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>186</v>
-      </c>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="3"/>
+      <c r="B38" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K38" s="24" t="s">
+        <v>266</v>
+      </c>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -4092,10 +4125,11 @@
     <hyperlink ref="I27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="I33" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="I37" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K38" r:id="rId16" xr:uid="{D57B73A2-2BE8-4D55-96C4-A684E517DB9F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -4111,36 +4145,36 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4148,39 +4182,39 @@
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
@@ -4188,45 +4222,45 @@
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="17"/>
       <c r="B10" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -4239,10 +4273,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -4250,7 +4284,7 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -4258,7 +4292,7 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -4266,7 +4300,7 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -4279,10 +4313,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -4290,7 +4324,7 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="17"/>
       <c r="B20" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -4298,7 +4332,7 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -4306,7 +4340,7 @@
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -4319,10 +4353,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>201</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>202</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -4330,7 +4364,7 @@
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -4338,7 +4372,7 @@
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
       <c r="B26" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -4351,10 +4385,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>204</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>205</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -4362,7 +4396,7 @@
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="17"/>
       <c r="B29" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -4370,7 +4404,7 @@
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -4383,10 +4417,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>207</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -4394,7 +4428,7 @@
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="17"/>
       <c r="B33" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -4465,22 +4499,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>213</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,22 +4522,22 @@
         <v>4</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>216</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4511,22 +4545,22 @@
         <v>6</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4534,22 +4568,22 @@
         <v>6</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>220</v>
-      </c>
       <c r="G4" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4557,22 +4591,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4580,22 +4614,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4603,22 +4637,22 @@
         <v>8</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4626,22 +4660,22 @@
         <v>8</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4649,22 +4683,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4672,22 +4706,22 @@
         <v>13</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4695,22 +4729,22 @@
         <v>14</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4718,22 +4752,22 @@
         <v>14</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4741,22 +4775,22 @@
         <v>18</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4764,22 +4798,22 @@
         <v>25</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4787,22 +4821,22 @@
         <v>25</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>232</v>
-      </c>
       <c r="G15" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4810,22 +4844,22 @@
         <v>26</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4833,22 +4867,22 @@
         <v>27</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4856,20 +4890,20 @@
         <v>29</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4877,22 +4911,22 @@
         <v>29</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>237</v>
-      </c>
       <c r="G19" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4900,22 +4934,22 @@
         <v>30</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4923,20 +4957,20 @@
         <v>32</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4944,22 +4978,22 @@
         <v>32</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4967,22 +5001,22 @@
         <v>33</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4990,22 +5024,22 @@
         <v>34</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5013,20 +5047,20 @@
         <v>35</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5034,22 +5068,22 @@
         <v>35</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5057,22 +5091,22 @@
         <v>35</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5080,20 +5114,20 @@
         <v>3</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5101,20 +5135,20 @@
         <v>3</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5122,22 +5156,22 @@
         <v>3</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G30" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5145,20 +5179,20 @@
         <v>4</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5166,20 +5200,20 @@
         <v>4</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5187,22 +5221,22 @@
         <v>4</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G33" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5210,20 +5244,20 @@
         <v>5</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5231,20 +5265,20 @@
         <v>5</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5252,22 +5286,22 @@
         <v>5</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E36" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G36" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5275,20 +5309,20 @@
         <v>6</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5296,20 +5330,20 @@
         <v>6</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G38" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5317,22 +5351,22 @@
         <v>6</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E39" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G39" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5340,20 +5374,20 @@
         <v>7</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5361,20 +5395,20 @@
         <v>7</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5382,22 +5416,22 @@
         <v>7</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E42" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G42" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5405,20 +5439,20 @@
         <v>8</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5426,20 +5460,20 @@
         <v>8</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5447,22 +5481,22 @@
         <v>8</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G45" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5470,20 +5504,20 @@
         <v>9</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5491,20 +5525,20 @@
         <v>9</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5512,22 +5546,22 @@
         <v>9</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E48" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G48" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5535,20 +5569,20 @@
         <v>10</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5556,20 +5590,20 @@
         <v>10</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5577,22 +5611,22 @@
         <v>10</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E51" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G51" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5600,20 +5634,20 @@
         <v>11</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5621,20 +5655,20 @@
         <v>11</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5642,22 +5676,22 @@
         <v>11</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E54" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>251</v>
-      </c>
       <c r="G54" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5665,20 +5699,20 @@
         <v>12</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5686,20 +5720,20 @@
         <v>12</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5707,22 +5741,22 @@
         <v>12</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5730,20 +5764,20 @@
         <v>13</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5751,20 +5785,20 @@
         <v>13</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5772,22 +5806,22 @@
         <v>13</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5795,20 +5829,20 @@
         <v>14</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5816,20 +5850,20 @@
         <v>14</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5837,22 +5871,22 @@
         <v>14</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5860,20 +5894,20 @@
         <v>15</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5881,20 +5915,20 @@
         <v>15</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5902,22 +5936,22 @@
         <v>15</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5925,20 +5959,20 @@
         <v>16</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D67" s="19"/>
       <c r="E67" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5946,20 +5980,20 @@
         <v>16</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5967,22 +6001,22 @@
         <v>16</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5990,20 +6024,20 @@
         <v>17</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" s="19"/>
       <c r="E70" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6011,20 +6045,20 @@
         <v>17</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6032,22 +6066,22 @@
         <v>17</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6055,20 +6089,20 @@
         <v>18</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" s="19"/>
       <c r="E73" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6076,20 +6110,20 @@
         <v>18</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6097,22 +6131,22 @@
         <v>18</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6120,20 +6154,20 @@
         <v>19</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" s="19"/>
       <c r="E76" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6141,20 +6175,20 @@
         <v>19</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" s="19"/>
       <c r="E77" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6162,22 +6196,22 @@
         <v>19</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6185,20 +6219,20 @@
         <v>20</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79" s="19"/>
       <c r="E79" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6206,20 +6240,20 @@
         <v>20</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" s="19"/>
       <c r="E80" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6227,22 +6261,22 @@
         <v>20</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6250,20 +6284,20 @@
         <v>21</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" s="19"/>
       <c r="E82" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6271,20 +6305,20 @@
         <v>21</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" s="19"/>
       <c r="E83" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6292,22 +6326,22 @@
         <v>21</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6315,20 +6349,20 @@
         <v>22</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" s="19"/>
       <c r="E85" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6336,20 +6370,20 @@
         <v>22</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" s="19"/>
       <c r="E86" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F86" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6357,22 +6391,22 @@
         <v>22</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6380,20 +6414,20 @@
         <v>23</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" s="19"/>
       <c r="E88" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F88" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6401,20 +6435,20 @@
         <v>23</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="19"/>
       <c r="E89" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F89" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6422,22 +6456,22 @@
         <v>23</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F90" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6445,20 +6479,20 @@
         <v>24</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" s="19"/>
       <c r="E91" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6466,20 +6500,20 @@
         <v>24</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="19"/>
       <c r="E92" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F92" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6487,22 +6521,22 @@
         <v>24</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6510,20 +6544,20 @@
         <v>25</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" s="19"/>
       <c r="E94" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F94" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6531,20 +6565,20 @@
         <v>25</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" s="19"/>
       <c r="E95" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6552,22 +6586,22 @@
         <v>25</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D96" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F96" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6575,20 +6609,20 @@
         <v>26</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6596,20 +6630,20 @@
         <v>26</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="19"/>
       <c r="E98" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F98" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6617,22 +6651,22 @@
         <v>26</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6640,22 +6674,22 @@
         <v>26</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6663,20 +6697,20 @@
         <v>27</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" s="19"/>
       <c r="E101" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6684,20 +6718,20 @@
         <v>27</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" s="19"/>
       <c r="E102" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F102" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6705,22 +6739,22 @@
         <v>27</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6728,20 +6762,20 @@
         <v>28</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C104" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104" s="19"/>
       <c r="E104" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F104" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6749,20 +6783,20 @@
         <v>28</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D105" s="19"/>
       <c r="E105" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F105" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6770,22 +6804,22 @@
         <v>28</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C106" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D106" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F106" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6793,20 +6827,20 @@
         <v>29</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" s="19"/>
       <c r="E107" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F107" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6814,20 +6848,20 @@
         <v>30</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" s="19"/>
       <c r="E108" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F108" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6835,20 +6869,20 @@
         <v>30</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D109" s="19"/>
       <c r="E109" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F109" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6856,22 +6890,22 @@
         <v>30</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F110" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E110" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F110" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G110" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6879,20 +6913,20 @@
         <v>31</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D111" s="19"/>
       <c r="E111" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6900,20 +6934,20 @@
         <v>31</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D112" s="19"/>
       <c r="E112" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F112" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6921,22 +6955,22 @@
         <v>31</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D113" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F113" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E113" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F113" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G113" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6944,20 +6978,20 @@
         <v>32</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D114" s="19"/>
       <c r="E114" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F114" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6965,22 +6999,22 @@
         <v>32</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D115" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F115" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E115" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F115" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G115" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6988,20 +7022,20 @@
         <v>33</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C116" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D116" s="19"/>
       <c r="E116" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F116" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7009,20 +7043,20 @@
         <v>33</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D117" s="19"/>
       <c r="E117" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F117" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7030,22 +7064,22 @@
         <v>33</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C118" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D118" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F118" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E118" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F118" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G118" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7053,20 +7087,20 @@
         <v>34</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D119" s="19"/>
       <c r="E119" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F119" s="19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7074,20 +7108,20 @@
         <v>34</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D120" s="19"/>
       <c r="E120" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F120" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7095,22 +7129,22 @@
         <v>34</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D121" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F121" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E121" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G121" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7118,20 +7152,20 @@
         <v>35</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D122" s="19"/>
       <c r="E122" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F122" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7139,22 +7173,22 @@
         <v>35</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D123" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F123" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E123" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F123" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G123" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7162,20 +7196,20 @@
         <v>36</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C124" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D124" s="19"/>
       <c r="E124" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F124" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7183,20 +7217,20 @@
         <v>36</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D125" s="19"/>
       <c r="E125" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7204,22 +7238,22 @@
         <v>36</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C126" s="19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F126" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G126" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7227,22 +7261,22 @@
         <v>36</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D127" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F127" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E127" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F127" s="19" t="s">
-        <v>254</v>
-      </c>
       <c r="G127" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/KI_Pflege_Anwendungsbeispiele.xlsx
+++ b/KI_Pflege_Anwendungsbeispiele.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acatechev.sharepoint.de/sites/Technologie/Freigegebene Dokumente/05 Lernende Systeme/03 AGs/AG 6 Gesundheit/WP KI und Pflegenotstand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{578BC691-77EE-41F0-B240-773D70F1C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{578BC691-77EE-41F0-B240-773D70F1C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C45B7A76-01E5-44C3-933D-A3472279CDFC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anwendungen" sheetId="1" r:id="rId1"/>
     <sheet name="Listen &amp; Hinweise" sheetId="3" r:id="rId2"/>
-    <sheet name="Änderungsprotokoll" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Änderungsprotokoll!$A$1:$G$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anwendungen!$A$1:$L$101</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Anwendungen!$1:$1</definedName>
     <definedName name="Kategorie">'Listen &amp; Hinweise'!$B$5:$B$7</definedName>
@@ -132,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="213">
   <si>
     <t>ID</t>
   </si>
@@ -823,168 +821,6 @@
     <t>Preprint</t>
   </si>
   <si>
-    <t>Projekt</t>
-  </si>
-  <si>
-    <t>Feld</t>
-  </si>
-  <si>
-    <t>Alt</t>
-  </si>
-  <si>
-    <t>Neu</t>
-  </si>
-  <si>
-    <t>Begründung</t>
-  </si>
-  <si>
-    <t>Sicherheit</t>
-  </si>
-  <si>
-    <t>Settingübergreifend</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Träger Universitätsklinikum Essen; Wundmanagement durch Pflegefachpersonen</t>
-  </si>
-  <si>
-    <t>Vorschlag – bitte prüfen</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'stationäre Pflege', Träger Charité</t>
-  </si>
-  <si>
-    <t>Sonstiges / unklar</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Risikovorhersage / Dashboard – gleiche Logik wie KIDELIR, EMRE-KI, ProSSpon</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Datenplattform u. a. mit Smart-Home-Geräten – eher häuslicher Bereich (unsicher)</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Datenplattform / Datenharmonisierung</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Sturzprophylaxe bei Pflegebedürftigen (typisch stationäre Langzeitpflege, unsicher)</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Risikovorhersage + Dashboard zur Planung – gleiche Logik wie ProSSpon</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'klinische Zusammenhänge', Behandlungsprozesse</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Sonstiges / unklar'): VR-Simulation für Pflegeberufe; kein eindeutiges Setting – Klinik als Annahme</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Sonstiges / unklar'): Tele-Pflegesystem mit Video-Sprechstunde (ambulant / Häuslichkeit)</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Video-Sprechstunden / Telepflege</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): AR-Übungstraining für Nutzende, eher häuslich / ambulant (unsicher)</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Wunderkennung am 'Point of Care'; Wundversorgung häufig ambulant (unsicher)</t>
-  </si>
-  <si>
-    <t>Mehrere KI-Typen</t>
-  </si>
-  <si>
-    <t>Haupttyp festgelegt (vorher 'Mehrere KI-Typen'): Bilderkennung von Wunden; Chatbot ist Zusatz (siehe Kommentar)</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Mobilisation / Mobilitätsunterstützung</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): soziale Betreuung / Prävention von Vereinsamung (Prozess-Landkarte: 'Pflegen')</t>
-  </si>
-  <si>
-    <t>Gemeinsames Projekt Fraunhofer IKS + ATOSS Software (Quelle: Fraunhofer-Artikel)</t>
-  </si>
-  <si>
-    <t>Pilot / Praxistest</t>
-  </si>
-  <si>
-    <t>Quelle formuliert in der Vergangenheit ('haben entwickelt'); Laufzeit unbekannt</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): Produktseite nennt zuerst 'Pflegeheime und ambulante Pflege'</t>
-  </si>
-  <si>
-    <t>Sitz des Anbieters: Belgien (Sitz Leuven)</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Sturz- und Bewegungserkennung – analog zu ally cares</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Sturz- und Aktivitätserkennung – analog zu ally cares</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Sturzerkennung / Sturzprävention – analog zu ally cares</t>
-  </si>
-  <si>
-    <t>Sitz des Anbieters: Schweiz (vermutet)</t>
-  </si>
-  <si>
-    <t>Hauptprozess festgelegt (vorher 'Sonstiges / unklar'): Bettausstieg / Sturz erkennen – analog zu ally cares</t>
-  </si>
-  <si>
-    <t>Radar-Sensorik + KI-Bewegungsanalyse (vorher 'Sonstiges / unklar')</t>
-  </si>
-  <si>
-    <t>EPWUFKI</t>
-  </si>
-  <si>
-    <t>Anbieter / Träger sitzt in Deutschland</t>
-  </si>
-  <si>
-    <t>sicher</t>
-  </si>
-  <si>
-    <t>Gefördertes Verbundprojekt (BMBF/BMFTR), Quelle: interaktive-technologien.de</t>
-  </si>
-  <si>
-    <t>Forschungsprojekt umgesetzt</t>
-  </si>
-  <si>
-    <t>Projektlaufzeit endete 2025 (laut Kommentar-Spalte)</t>
-  </si>
-  <si>
-    <t>Kommerzielles Produkt / Anbieter</t>
-  </si>
-  <si>
-    <t>Im laufenden Einsatz</t>
-  </si>
-  <si>
-    <t>Kommerzielles Produkt am Markt</t>
-  </si>
-  <si>
-    <t>Projektlaufzeit läuft noch (laut Kommentar-Spalte)</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Sonstiges / unklar'): Rollator für selbstständige Mobilität im urbanen Raum / Weg nach Hause</t>
-  </si>
-  <si>
-    <t>Laufzeit 11/2024 – 10/2026: endet in diesen Tagen, ggf. bald auf 'Abgeschlossen' setzen</t>
-  </si>
-  <si>
-    <t>Projektlaufzeit endete 02/2026</t>
-  </si>
-  <si>
-    <t>Sitz des Anbieters: Vereinigtes Königreich (UK)</t>
-  </si>
-  <si>
-    <t>Sitz des Anbieters: Australien</t>
-  </si>
-  <si>
-    <t>Sitz des Anbieters: USA</t>
-  </si>
-  <si>
-    <t>Hauptsetting festgelegt (vorher 'Settingübergreifend'): 'mehrere Bewohner in einer Aufnahme'</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Digital Case Manager-A Data-Driven Tool to Support Family Caregivers with Initial Guidance </t>
   </si>
   <si>
@@ -1004,7 +840,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1078,10 +914,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1114,7 +946,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1140,21 +972,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1206,15 +1029,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1692,7 +1506,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1805,7 +1619,7 @@
       <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -1881,10 +1695,10 @@
       <c r="E7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -1919,10 +1733,10 @@
       <c r="E8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -1957,10 +1771,10 @@
       <c r="E9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="18" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -2071,7 +1885,7 @@
       <c r="E12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -2147,7 +1961,7 @@
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="18" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -2185,10 +1999,10 @@
       <c r="E15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="18" t="s">
         <v>75</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -2337,7 +2151,7 @@
       <c r="E19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -2603,13 +2417,13 @@
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="18" t="s">
         <v>17</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -2644,7 +2458,7 @@
       <c r="F27" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -2682,7 +2496,7 @@
       <c r="F28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G28" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -2764,7 +2578,7 @@
       <c r="H30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="18" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="15" t="s">
@@ -2793,7 +2607,7 @@
       <c r="E31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="18" t="s">
         <v>47</v>
       </c>
       <c r="G31" s="4" t="s">
@@ -2862,13 +2676,13 @@
       <c r="D33" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="18" t="s">
         <v>166</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H33" s="4" t="s">
@@ -2904,7 +2718,7 @@
       <c r="F34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -2940,7 +2754,7 @@
       <c r="F35" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="21" t="s">
+      <c r="G35" s="18" t="s">
         <v>95</v>
       </c>
       <c r="H35" s="4" t="s">
@@ -2970,16 +2784,16 @@
       <c r="D36" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="18" t="s">
         <v>166</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="21" t="s">
+      <c r="G36" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="18" t="s">
         <v>17</v>
       </c>
       <c r="I36" s="2" t="s">
@@ -3034,13 +2848,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>14</v>
@@ -3060,8 +2874,8 @@
       <c r="J38" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="K38" s="24" t="s">
-        <v>266</v>
+      <c r="K38" s="21" t="s">
+        <v>212</v>
       </c>
       <c r="L38" s="2"/>
     </row>
@@ -4479,2808 +4293,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="80" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
-        <v>4</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
-        <v>6</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
-        <v>6</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>7</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>7</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <v>8</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
-        <v>8</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
-        <v>11</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
-        <v>13</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
-        <v>14</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
-        <v>14</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
-        <v>18</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
-        <v>25</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <v>25</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
-        <v>26</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
-        <v>27</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
-        <v>29</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
-        <v>29</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
-        <v>30</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
-        <v>32</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
-        <v>32</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
-        <v>33</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
-        <v>34</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
-        <v>35</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19">
-        <v>35</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19">
-        <v>35</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19">
-        <v>3</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19">
-        <v>3</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19">
-        <v>3</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
-        <v>4</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19">
-        <v>4</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
-        <v>4</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
-        <v>5</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19">
-        <v>5</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
-        <v>5</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="19">
-        <v>6</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="19">
-        <v>6</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="19">
-        <v>6</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
-        <v>7</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="19">
-        <v>7</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="19">
-        <v>7</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="19">
-        <v>8</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="19">
-        <v>8</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="19">
-        <v>8</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="19">
-        <v>9</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="19">
-        <v>9</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="19">
-        <v>9</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19">
-        <v>10</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="19">
-        <v>10</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="19">
-        <v>10</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="19">
-        <v>11</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="19">
-        <v>11</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="19">
-        <v>11</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="19">
-        <v>12</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="19">
-        <v>12</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="19">
-        <v>12</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G57" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="19">
-        <v>13</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G58" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="19">
-        <v>13</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
-        <v>13</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G60" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="19">
-        <v>14</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="19">
-        <v>14</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G62" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="19">
-        <v>14</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="19">
-        <v>15</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="19">
-        <v>15</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="19">
-        <v>15</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G66" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="19">
-        <v>16</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="19">
-        <v>16</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F68" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="19">
-        <v>16</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="19">
-        <v>17</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="19">
-        <v>17</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="19">
-        <v>17</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="19">
-        <v>18</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G73" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="19">
-        <v>18</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C74" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G74" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="19">
-        <v>18</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F75" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G75" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="19">
-        <v>19</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G76" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="19">
-        <v>19</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="19">
-        <v>19</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F78" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G78" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="19">
-        <v>20</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G79" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="19">
-        <v>20</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F80" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G80" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="19">
-        <v>20</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F81" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G81" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="19">
-        <v>21</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G82" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="19">
-        <v>21</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="19">
-        <v>21</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C84" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F84" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="19">
-        <v>22</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G85" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="19">
-        <v>22</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F86" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G86" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="19">
-        <v>22</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F87" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G87" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="19">
-        <v>23</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G88" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="19">
-        <v>23</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F89" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G89" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="19">
-        <v>23</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F90" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G90" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="19">
-        <v>24</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G91" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="19">
-        <v>24</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C92" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F92" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G92" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="19">
-        <v>24</v>
-      </c>
-      <c r="B93" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F93" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G93" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="19">
-        <v>25</v>
-      </c>
-      <c r="B94" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F94" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G94" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="19">
-        <v>25</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="19"/>
-      <c r="E95" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F95" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G95" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="19">
-        <v>25</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F96" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="19">
-        <v>26</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="C97" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F97" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G97" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="19">
-        <v>26</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F98" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G98" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="19">
-        <v>26</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D99" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E99" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F99" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="G99" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="19">
-        <v>26</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="C100" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E100" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F100" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G100" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="19">
-        <v>27</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G101" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="19">
-        <v>27</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C102" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F102" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G102" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="19">
-        <v>27</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F103" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="19">
-        <v>28</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="19"/>
-      <c r="E104" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G104" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="19">
-        <v>28</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F105" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G105" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="19">
-        <v>28</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E106" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="F106" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="G106" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="19">
-        <v>29</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="19"/>
-      <c r="E107" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F107" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G107" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="19">
-        <v>30</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C108" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="19"/>
-      <c r="E108" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G108" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="19">
-        <v>30</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D109" s="19"/>
-      <c r="E109" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F109" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G109" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="19">
-        <v>30</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E110" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F110" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G110" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="19">
-        <v>31</v>
-      </c>
-      <c r="B111" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="F111" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="G111" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="19">
-        <v>31</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C112" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F112" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G112" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="19">
-        <v>31</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E113" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F113" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G113" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="19">
-        <v>32</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C114" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D114" s="19"/>
-      <c r="E114" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F114" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G114" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="19">
-        <v>32</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E115" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F115" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G115" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="19">
-        <v>33</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C116" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="19"/>
-      <c r="E116" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="F116" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="G116" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="19">
-        <v>33</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C117" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D117" s="19"/>
-      <c r="E117" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F117" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G117" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="19">
-        <v>33</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C118" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F118" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="19">
-        <v>34</v>
-      </c>
-      <c r="B119" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="19"/>
-      <c r="E119" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="G119" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="19">
-        <v>34</v>
-      </c>
-      <c r="B120" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C120" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D120" s="19"/>
-      <c r="E120" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F120" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G120" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="19">
-        <v>34</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C121" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G121" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="19">
-        <v>35</v>
-      </c>
-      <c r="B122" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C122" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D122" s="19"/>
-      <c r="E122" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G122" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="19">
-        <v>35</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E123" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F123" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G123" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="19">
-        <v>36</v>
-      </c>
-      <c r="B124" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C124" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="19"/>
-      <c r="E124" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F124" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="G124" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="19">
-        <v>36</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C125" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D125" s="19"/>
-      <c r="E125" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F125" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G125" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="19">
-        <v>36</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D126" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="E126" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F126" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="G126" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="19">
-        <v>36</v>
-      </c>
-      <c r="B127" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C127" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E127" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="F127" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G127" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G127" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/KI_Pflege_Anwendungsbeispiele.xlsx
+++ b/KI_Pflege_Anwendungsbeispiele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acatechev.sharepoint.de/sites/Technologie/Freigegebene Dokumente/05 Lernende Systeme/03 AGs/AG 6 Gesundheit/WP KI und Pflegenotstand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{578BC691-77EE-41F0-B240-773D70F1C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C45B7A76-01E5-44C3-933D-A3472279CDFC}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{578BC691-77EE-41F0-B240-773D70F1C910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E997A82-2BA8-41A3-A13F-3BBB49EF16F0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -830,10 +830,10 @@
     <t>Paul Wunderlich, Frauke Wiegräbe, Helene Dörksen</t>
   </si>
   <si>
-    <t>Anbieter / Autoren</t>
-  </si>
-  <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/36673969/</t>
+  </si>
+  <si>
+    <t>Anbieter / Träger</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1506,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2875,7 +2875,7 @@
         <v>206</v>
       </c>
       <c r="K38" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L38" s="2"/>
     </row>
@@ -4293,4 +4293,323 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010063107CA8B5A7434FA88AAD429DD09C74" ma:contentTypeVersion="21" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="85d3e4c670172debd402798e1f9f0405">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c" xmlns:ns3="cd56f89b-ac27-4c6b-9540-7772d6c08fe7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="07be3d46663b0142a603846ae7b31bbe" ns2:_="" ns3:_="">
+    <xsd:import namespace="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c"/>
+    <xsd:import namespace="cd56f89b-ac27-4c6b-9540-7772d6c08fe7"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="18" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="19" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4fc58ff6-2a3f-40a3-8d32-e116a35ec156" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cd56f89b-ac27-4c6b-9540-7772d6c08fe7" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f5d2cfef-bc52-4180-8fb0-073759876f91}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="cd56f89b-ac27-4c6b-9540-7772d6c08fe7">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cd56f89b-ac27-4c6b-9540-7772d6c08fe7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE02F234-2B29-4DC9-AEED-EB57AE9A0545}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c"/>
+    <ds:schemaRef ds:uri="cd56f89b-ac27-4c6b-9540-7772d6c08fe7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0D7C7F-08FC-47C5-9FDF-644B067E771B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2f7555ce-aa9e-4c12-9ea3-19b2eff72f7c"/>
+    <ds:schemaRef ds:uri="cd56f89b-ac27-4c6b-9540-7772d6c08fe7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED1BA9B3-E770-4AAB-BB1F-50D15DB54E3D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>